--- a/NPW_ephys/ramp_stats.xlsx
+++ b/NPW_ephys/ramp_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/caom/Documents/negative_parental_switch/NPW_ephys/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB4AB45-05D1-7443-9EA1-5DAFBC6ED776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26660C9-5EBB-7446-9C87-D175839E689F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37880" yWindow="2020" windowWidth="26340" windowHeight="14760" activeTab="7" xr2:uid="{870C7E5E-6E44-FF4A-8C5E-BDACA255F530}"/>
+    <workbookView xWindow="37880" yWindow="2020" windowWidth="26340" windowHeight="14760" xr2:uid="{870C7E5E-6E44-FF4A-8C5E-BDACA255F530}"/>
   </bookViews>
   <sheets>
     <sheet name="Fig.3d" sheetId="7" r:id="rId1"/>
